--- a/Документация/Отладка.xlsx
+++ b/Документация/Отладка.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Выкса\Дезоксидация\Аналитическая модель прогноза расхода\Документация\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9480BE12-CDE0-4E3C-B28D-50982A44A843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{141D0BD2-0458-4755-9C07-5A03E27DAD31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -368,7 +368,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C107"/>
+  <dimension ref="A1:C108"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
@@ -432,11 +432,11 @@
         <v>2</v>
       </c>
       <c r="B9">
-        <f t="shared" ref="B9:B72" si="0">A9*$B$2/10</f>
+        <f t="shared" ref="B9:B73" si="0">A9*$B$2/10</f>
         <v>1.2</v>
       </c>
       <c r="C9">
-        <f t="shared" ref="C9:C72" si="1">ROUNDDOWN(B9,0)</f>
+        <f t="shared" ref="C9:C73" si="1">ROUNDDOWN(B9,0)</f>
         <v>1</v>
       </c>
     </row>
@@ -468,24 +468,24 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B13">
         <f t="shared" si="0"/>
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
@@ -494,24 +494,24 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B14">
         <f t="shared" si="0"/>
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B15">
         <f t="shared" si="0"/>
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="C15">
         <f t="shared" si="1"/>
@@ -520,37 +520,37 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B16">
         <f t="shared" si="0"/>
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="C16">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B17">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="C17">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18">
         <f t="shared" si="0"/>
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="C18">
         <f t="shared" si="1"/>
@@ -559,24 +559,24 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19">
         <f t="shared" si="0"/>
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="C19">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B20">
         <f t="shared" si="0"/>
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="C20">
         <f t="shared" si="1"/>
@@ -585,37 +585,37 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B21">
         <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="C21">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B22">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="C22">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B23">
         <f t="shared" si="0"/>
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="C23">
         <f t="shared" si="1"/>
@@ -624,24 +624,24 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B24">
         <f t="shared" si="0"/>
-        <v>10.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="C24">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25">
         <f t="shared" si="0"/>
-        <v>10.8</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="C25">
         <f t="shared" si="1"/>
@@ -650,37 +650,37 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B26">
         <f t="shared" si="0"/>
-        <v>11.4</v>
+        <v>10.8</v>
       </c>
       <c r="C26">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B27">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11.4</v>
       </c>
       <c r="C27">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B28">
         <f t="shared" si="0"/>
-        <v>12.6</v>
+        <v>12</v>
       </c>
       <c r="C28">
         <f t="shared" si="1"/>
@@ -689,24 +689,24 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B29">
         <f t="shared" si="0"/>
-        <v>13.2</v>
+        <v>12.6</v>
       </c>
       <c r="C29">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B30">
         <f t="shared" si="0"/>
-        <v>13.8</v>
+        <v>13.2</v>
       </c>
       <c r="C30">
         <f t="shared" si="1"/>
@@ -715,37 +715,37 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B31">
         <f t="shared" si="0"/>
-        <v>14.4</v>
+        <v>13.8</v>
       </c>
       <c r="C31">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B32">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>14.4</v>
       </c>
       <c r="C32">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B33">
         <f t="shared" si="0"/>
-        <v>15.6</v>
+        <v>15</v>
       </c>
       <c r="C33">
         <f t="shared" si="1"/>
@@ -754,24 +754,24 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B34">
         <f t="shared" si="0"/>
-        <v>16.2</v>
+        <v>15.6</v>
       </c>
       <c r="C34">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B35">
         <f t="shared" si="0"/>
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="C35">
         <f t="shared" si="1"/>
@@ -780,37 +780,37 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B36">
         <f t="shared" si="0"/>
-        <v>17.399999999999999</v>
+        <v>16.8</v>
       </c>
       <c r="C36">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B37">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="C37">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B38">
         <f t="shared" si="0"/>
-        <v>18.600000000000001</v>
+        <v>18</v>
       </c>
       <c r="C38">
         <f t="shared" si="1"/>
@@ -819,24 +819,24 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B39">
         <f t="shared" si="0"/>
-        <v>19.2</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="C39">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B40">
         <f t="shared" si="0"/>
-        <v>19.8</v>
+        <v>19.2</v>
       </c>
       <c r="C40">
         <f t="shared" si="1"/>
@@ -845,37 +845,37 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B41">
         <f t="shared" si="0"/>
-        <v>20.399999999999999</v>
+        <v>19.8</v>
       </c>
       <c r="C41">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B42">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="C42">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B43">
         <f t="shared" si="0"/>
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="C43">
         <f t="shared" si="1"/>
@@ -884,24 +884,24 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B44">
         <f t="shared" si="0"/>
-        <v>22.2</v>
+        <v>21.6</v>
       </c>
       <c r="C44">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B45">
         <f t="shared" si="0"/>
-        <v>22.8</v>
+        <v>22.2</v>
       </c>
       <c r="C45">
         <f t="shared" si="1"/>
@@ -910,37 +910,37 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B46">
         <f t="shared" si="0"/>
-        <v>23.4</v>
+        <v>22.8</v>
       </c>
       <c r="C46">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B47">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>23.4</v>
       </c>
       <c r="C47">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48">
         <f t="shared" si="0"/>
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="C48">
         <f t="shared" si="1"/>
@@ -949,24 +949,24 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B49">
         <f t="shared" si="0"/>
-        <v>25.2</v>
+        <v>24.6</v>
       </c>
       <c r="C49">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B50">
         <f t="shared" si="0"/>
-        <v>25.8</v>
+        <v>25.2</v>
       </c>
       <c r="C50">
         <f t="shared" si="1"/>
@@ -975,37 +975,37 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B51">
         <f t="shared" si="0"/>
-        <v>26.4</v>
+        <v>25.8</v>
       </c>
       <c r="C51">
         <f t="shared" si="1"/>
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B52">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>26.4</v>
       </c>
       <c r="C52">
         <f t="shared" si="1"/>
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B53">
         <f t="shared" si="0"/>
-        <v>27.6</v>
+        <v>27</v>
       </c>
       <c r="C53">
         <f t="shared" si="1"/>
@@ -1014,24 +1014,24 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B54">
         <f t="shared" si="0"/>
-        <v>28.2</v>
+        <v>27.6</v>
       </c>
       <c r="C54">
         <f t="shared" si="1"/>
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B55">
         <f t="shared" si="0"/>
-        <v>28.8</v>
+        <v>28.2</v>
       </c>
       <c r="C55">
         <f t="shared" si="1"/>
@@ -1040,37 +1040,37 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B56">
         <f t="shared" si="0"/>
-        <v>29.4</v>
+        <v>28.8</v>
       </c>
       <c r="C56">
         <f t="shared" si="1"/>
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B57">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>29.4</v>
       </c>
       <c r="C57">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B58">
         <f t="shared" si="0"/>
-        <v>30.6</v>
+        <v>30</v>
       </c>
       <c r="C58">
         <f t="shared" si="1"/>
@@ -1079,24 +1079,24 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B59">
         <f t="shared" si="0"/>
-        <v>31.2</v>
+        <v>30.6</v>
       </c>
       <c r="C59">
         <f t="shared" si="1"/>
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B60">
         <f t="shared" si="0"/>
-        <v>31.8</v>
+        <v>31.2</v>
       </c>
       <c r="C60">
         <f t="shared" si="1"/>
@@ -1105,37 +1105,37 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B61">
         <f t="shared" si="0"/>
-        <v>32.4</v>
+        <v>31.8</v>
       </c>
       <c r="C61">
         <f t="shared" si="1"/>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B62">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>32.4</v>
       </c>
       <c r="C62">
         <f t="shared" si="1"/>
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B63">
         <f t="shared" si="0"/>
-        <v>33.6</v>
+        <v>33</v>
       </c>
       <c r="C63">
         <f t="shared" si="1"/>
@@ -1144,24 +1144,24 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B64">
         <f t="shared" si="0"/>
-        <v>34.200000000000003</v>
+        <v>33.6</v>
       </c>
       <c r="C64">
         <f t="shared" si="1"/>
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B65">
         <f t="shared" si="0"/>
-        <v>34.799999999999997</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="C65">
         <f t="shared" si="1"/>
@@ -1170,37 +1170,37 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B66">
         <f t="shared" si="0"/>
-        <v>35.4</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="C66">
         <f t="shared" si="1"/>
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B67">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>35.4</v>
       </c>
       <c r="C67">
         <f t="shared" si="1"/>
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B68">
         <f t="shared" si="0"/>
-        <v>36.6</v>
+        <v>36</v>
       </c>
       <c r="C68">
         <f t="shared" si="1"/>
@@ -1209,24 +1209,24 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B69">
         <f t="shared" si="0"/>
-        <v>37.200000000000003</v>
+        <v>36.6</v>
       </c>
       <c r="C69">
         <f t="shared" si="1"/>
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B70">
         <f t="shared" si="0"/>
-        <v>37.799999999999997</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="C70">
         <f t="shared" si="1"/>
@@ -1235,63 +1235,63 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B71">
         <f t="shared" si="0"/>
-        <v>38.4</v>
+        <v>37.799999999999997</v>
       </c>
       <c r="C71">
         <f t="shared" si="1"/>
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B72">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>38.4</v>
       </c>
       <c r="C72">
         <f t="shared" si="1"/>
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B73">
-        <f t="shared" ref="B73:B107" si="2">A73*$B$2/10</f>
-        <v>39.6</v>
+        <f t="shared" si="0"/>
+        <v>39</v>
       </c>
       <c r="C73">
-        <f t="shared" ref="C73:C107" si="3">ROUNDDOWN(B73,0)</f>
+        <f t="shared" si="1"/>
         <v>39</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B74">
-        <f t="shared" si="2"/>
-        <v>40.200000000000003</v>
+        <f t="shared" ref="B74:B108" si="2">A74*$B$2/10</f>
+        <v>39.6</v>
       </c>
       <c r="C74">
-        <f t="shared" si="3"/>
-        <v>40</v>
+        <f t="shared" ref="C74:C108" si="3">ROUNDDOWN(B74,0)</f>
+        <v>39</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B75">
         <f t="shared" si="2"/>
-        <v>40.799999999999997</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="C75">
         <f t="shared" si="3"/>
@@ -1300,37 +1300,37 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B76">
         <f t="shared" si="2"/>
-        <v>41.4</v>
+        <v>40.799999999999997</v>
       </c>
       <c r="C76">
         <f t="shared" si="3"/>
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B77">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>41.4</v>
       </c>
       <c r="C77">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B78">
         <f t="shared" si="2"/>
-        <v>42.6</v>
+        <v>42</v>
       </c>
       <c r="C78">
         <f t="shared" si="3"/>
@@ -1339,24 +1339,24 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B79">
         <f t="shared" si="2"/>
-        <v>43.2</v>
+        <v>42.6</v>
       </c>
       <c r="C79">
         <f t="shared" si="3"/>
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B80">
         <f t="shared" si="2"/>
-        <v>43.8</v>
+        <v>43.2</v>
       </c>
       <c r="C80">
         <f t="shared" si="3"/>
@@ -1365,37 +1365,37 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B81">
         <f t="shared" si="2"/>
-        <v>44.4</v>
+        <v>43.8</v>
       </c>
       <c r="C81">
         <f t="shared" si="3"/>
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B82">
         <f t="shared" si="2"/>
-        <v>45</v>
+        <v>44.4</v>
       </c>
       <c r="C82">
         <f t="shared" si="3"/>
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B83">
         <f t="shared" si="2"/>
-        <v>45.6</v>
+        <v>45</v>
       </c>
       <c r="C83">
         <f t="shared" si="3"/>
@@ -1404,24 +1404,24 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B84">
         <f t="shared" si="2"/>
-        <v>46.2</v>
+        <v>45.6</v>
       </c>
       <c r="C84">
         <f t="shared" si="3"/>
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B85">
         <f t="shared" si="2"/>
-        <v>46.8</v>
+        <v>46.2</v>
       </c>
       <c r="C85">
         <f t="shared" si="3"/>
@@ -1430,37 +1430,37 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B86">
         <f t="shared" si="2"/>
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="C86">
         <f t="shared" si="3"/>
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B87">
         <f t="shared" si="2"/>
-        <v>48</v>
+        <v>47.4</v>
       </c>
       <c r="C87">
         <f t="shared" si="3"/>
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B88">
         <f t="shared" si="2"/>
-        <v>48.6</v>
+        <v>48</v>
       </c>
       <c r="C88">
         <f t="shared" si="3"/>
@@ -1469,24 +1469,24 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B89">
         <f t="shared" si="2"/>
-        <v>49.2</v>
+        <v>48.6</v>
       </c>
       <c r="C89">
         <f t="shared" si="3"/>
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B90">
         <f t="shared" si="2"/>
-        <v>49.8</v>
+        <v>49.2</v>
       </c>
       <c r="C90">
         <f t="shared" si="3"/>
@@ -1495,37 +1495,37 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B91">
         <f t="shared" si="2"/>
-        <v>50.4</v>
+        <v>49.8</v>
       </c>
       <c r="C91">
         <f t="shared" si="3"/>
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B92">
         <f t="shared" si="2"/>
-        <v>51</v>
+        <v>50.4</v>
       </c>
       <c r="C92">
         <f t="shared" si="3"/>
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B93">
         <f t="shared" si="2"/>
-        <v>51.6</v>
+        <v>51</v>
       </c>
       <c r="C93">
         <f t="shared" si="3"/>
@@ -1534,24 +1534,24 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B94">
         <f t="shared" si="2"/>
-        <v>52.2</v>
+        <v>51.6</v>
       </c>
       <c r="C94">
         <f t="shared" si="3"/>
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B95">
         <f t="shared" si="2"/>
-        <v>52.8</v>
+        <v>52.2</v>
       </c>
       <c r="C95">
         <f t="shared" si="3"/>
@@ -1560,37 +1560,37 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B96">
         <f t="shared" si="2"/>
-        <v>53.4</v>
+        <v>52.8</v>
       </c>
       <c r="C96">
         <f t="shared" si="3"/>
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B97">
         <f t="shared" si="2"/>
-        <v>54</v>
+        <v>53.4</v>
       </c>
       <c r="C97">
         <f t="shared" si="3"/>
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B98">
         <f t="shared" si="2"/>
-        <v>54.6</v>
+        <v>54</v>
       </c>
       <c r="C98">
         <f t="shared" si="3"/>
@@ -1599,24 +1599,24 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B99">
         <f t="shared" si="2"/>
-        <v>55.2</v>
+        <v>54.6</v>
       </c>
       <c r="C99">
         <f t="shared" si="3"/>
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B100">
         <f t="shared" si="2"/>
-        <v>55.8</v>
+        <v>55.2</v>
       </c>
       <c r="C100">
         <f t="shared" si="3"/>
@@ -1625,37 +1625,37 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B101">
         <f t="shared" si="2"/>
-        <v>56.4</v>
+        <v>55.8</v>
       </c>
       <c r="C101">
         <f t="shared" si="3"/>
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B102">
         <f t="shared" si="2"/>
-        <v>57</v>
+        <v>56.4</v>
       </c>
       <c r="C102">
         <f t="shared" si="3"/>
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B103">
         <f t="shared" si="2"/>
-        <v>57.6</v>
+        <v>57</v>
       </c>
       <c r="C103">
         <f t="shared" si="3"/>
@@ -1664,24 +1664,24 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B104">
         <f t="shared" si="2"/>
-        <v>58.2</v>
+        <v>57.6</v>
       </c>
       <c r="C104">
         <f t="shared" si="3"/>
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B105">
         <f t="shared" si="2"/>
-        <v>58.8</v>
+        <v>58.2</v>
       </c>
       <c r="C105">
         <f t="shared" si="3"/>
@@ -1690,26 +1690,39 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B106">
         <f t="shared" si="2"/>
-        <v>59.4</v>
+        <v>58.8</v>
       </c>
       <c r="C106">
         <f t="shared" si="3"/>
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107">
+        <v>99</v>
+      </c>
+      <c r="B107">
+        <f t="shared" si="2"/>
+        <v>59.4</v>
+      </c>
+      <c r="C107">
+        <f t="shared" si="3"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108">
         <v>100</v>
       </c>
-      <c r="B107">
+      <c r="B108">
         <f t="shared" si="2"/>
         <v>60</v>
       </c>
-      <c r="C107">
+      <c r="C108">
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
